--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\GDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/elec/GDPbES/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8F5F98-CF08-104B-9BCB-F3FB0C019E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="22995" windowHeight="11055"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="GDPbES" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -124,7 +138,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -189,9 +203,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -229,9 +243,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,7 +280,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -301,7 +315,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -474,86 +488,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -565,18 +579,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>32</v>
       </c>
@@ -689,7 +703,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -837,1191 +851,1191 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:R14" si="1">$B3</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AK3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
         <f t="shared" ref="D9:AK14" si="2">$B9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK9">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -2169,7 +2183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2317,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2465,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2613,12 +2627,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15">
-        <f>B11</f>
         <v>0</v>
       </c>
       <c r="C15">
@@ -2762,12 +2775,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16">
-        <f>B11</f>
         <v>0</v>
       </c>
       <c r="C16">
@@ -2911,153 +2923,152 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17">
-        <f>B9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:AK17" si="5">C9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
